--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.25240424214471</v>
+        <v>6.703515689348516</v>
       </c>
       <c r="D2" t="n">
-        <v>41.67685178184549</v>
+        <v>6.772488414549891</v>
       </c>
       <c r="E2" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F2" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.34826459136004</v>
+        <v>11.91909299609601</v>
       </c>
       <c r="D3" t="n">
-        <v>73.76598079161258</v>
+        <v>11.98697187863704</v>
       </c>
       <c r="E3" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F3" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.17387627509424</v>
+        <v>5.553254894702814</v>
       </c>
       <c r="D4" t="n">
-        <v>33.74917766835996</v>
+        <v>5.484241371108493</v>
       </c>
       <c r="E4" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F4" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.19420725668478</v>
+        <v>2.794058679211276</v>
       </c>
       <c r="D5" t="n">
-        <v>17.58373311639073</v>
+        <v>2.857356631413494</v>
       </c>
       <c r="E5" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F5" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.33351560830711</v>
+        <v>2.166696286349905</v>
       </c>
       <c r="D6" t="n">
-        <v>13.23564251216168</v>
+        <v>2.150791908226272</v>
       </c>
       <c r="E6" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F6" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.40278939424236</v>
+        <v>3.477953276564384</v>
       </c>
       <c r="D7" t="n">
-        <v>21.05002857972206</v>
+        <v>3.420629644204835</v>
       </c>
       <c r="E7" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F7" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>51.61254551671049</v>
+        <v>8.387038646465456</v>
       </c>
       <c r="D8" t="n">
-        <v>52.72951563707496</v>
+        <v>8.568546291024681</v>
       </c>
       <c r="E8" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F8" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.33381357558786</v>
+        <v>2.491744706033026</v>
       </c>
       <c r="D9" t="n">
-        <v>9.83225275080898</v>
+        <v>1.597741072006459</v>
       </c>
       <c r="E9" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F9" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.15684099669405</v>
+        <v>4.737986661962784</v>
       </c>
       <c r="D10" t="n">
-        <v>46.61538094575558</v>
+        <v>7.574999403685281</v>
       </c>
       <c r="E10" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F10" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.975857493656282</v>
+        <v>0.9710768427191457</v>
       </c>
       <c r="D11" t="n">
-        <v>7.745805316189211</v>
+        <v>1.258693363880747</v>
       </c>
       <c r="E11" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F11" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.86549326330411</v>
+        <v>2.578142655286918</v>
       </c>
       <c r="D12" t="n">
-        <v>26.97165001612099</v>
+        <v>4.382893127619662</v>
       </c>
       <c r="E12" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F12" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.07291435475143</v>
+        <v>5.211848582647108</v>
       </c>
       <c r="D13" t="n">
-        <v>67.41244364608249</v>
+        <v>10.95452209248841</v>
       </c>
       <c r="E13" t="n">
-        <v>18.24773971841532</v>
+        <v>2.965257704242489</v>
       </c>
       <c r="F13" t="n">
-        <v>21.32328237806442</v>
+        <v>3.465033386435467</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
